--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488303_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488303_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5883</v>
+        <v>2.3924</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8158</v>
+        <v>3.6199</v>
       </c>
       <c r="F2" t="n">
         <v>-1.2275</v>
@@ -610,10 +610,10 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.097</v>
+        <v>-0.0989</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0174</v>
+        <v>-0.1784</v>
       </c>
       <c r="U2" t="n">
         <v>0.0796</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4645</v>
+        <v>1.3184</v>
       </c>
       <c r="E3" t="n">
-        <v>1.978</v>
+        <v>1.6842</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5135</v>
+        <v>-0.3657</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1333</v>
@@ -688,13 +688,13 @@
         <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2378</v>
+        <v>0.0917</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0584</v>
+        <v>-0.3522</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2962</v>
+        <v>0.4439</v>
       </c>
       <c r="V3" t="n">
         <v>0.063</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0772</v>
+        <v>0.7599</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7692</v>
+        <v>5.2796</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.692</v>
+        <v>-4.5197</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1552</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6882</v>
+        <v>0.3709</v>
       </c>
       <c r="T4" t="n">
-        <v>1.016</v>
+        <v>0.5264</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3278</v>
+        <v>-0.1555</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0587</v>
+        <v>-0.3279</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2946</v>
+        <v>2.0008</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3533</v>
+        <v>-2.3286</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1192</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7663</v>
+        <v>0.4971</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6703</v>
+        <v>0.3765</v>
       </c>
       <c r="U6" t="n">
-        <v>0.096</v>
+        <v>0.1206</v>
       </c>
       <c r="V6" t="n">
         <v>2.5177</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-1.087</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3256</v>
+        <v>0.1791</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-1.2661</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5592</v>
+        <v>-0.0439</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4241</v>
+        <v>-0.1039</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1351</v>
+        <v>0.0599</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4192</v>
+        <v>0.1474</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3778</v>
+        <v>0.0644</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>0.0829</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9784</v>
+        <v>-0.1913</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8018</v>
+        <v>-0.1683</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1766</v>
+        <v>-0.023</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1853</v>
+        <v>0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9093</v>
+        <v>0.0305</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1816</v>
+        <v>0.0317</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7277</v>
+        <v>-0.0012</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1105</v>
+        <v>-1.3963</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0168</v>
+        <v>-0.2801</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0937</v>
+        <v>-1.1163</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0439</v>
+        <v>-1.2428</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1039</v>
+        <v>-1.3028</v>
       </c>
       <c r="I8" t="n">
         <v>0.0599</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1474</v>
+        <v>0.1903</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0644</v>
+        <v>0.1074</v>
       </c>
       <c r="L8" t="n">
         <v>0.0829</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1913</v>
+        <v>-1.4331</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1683</v>
+        <v>-1.4101</v>
       </c>
       <c r="O8" t="n">
         <v>-0.023</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.007</v>
+        <v>0.4685</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1641</v>
+        <v>0.4561</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1711</v>
+        <v>0.0124</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2589</v>
+        <v>-0.2514</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2589</v>
+        <v>-0.2514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.886</v>
+        <v>-1.4485</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.7173</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1163</v>
+        <v>-0.7312</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2428</v>
+        <v>-1.5592</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3028</v>
+        <v>-1.4241</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0599</v>
+        <v>-0.1351</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1903</v>
+        <v>0.4192</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1074</v>
+        <v>0.3778</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0829</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4331</v>
+        <v>-1.9784</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4101</v>
+        <v>-1.8018</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.023</v>
+        <v>-0.1766</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0211</v>
+        <v>0.296</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0336</v>
+        <v>-0.2101</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0124</v>
+        <v>0.5061</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2514</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3152</v>
+        <v>-1.9496</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2357</v>
+        <v>-0.4181</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0795</v>
+        <v>-1.5315</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3175</v>
+        <v>-1.521</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7462</v>
+        <v>-0.1648</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5714</v>
+        <v>-1.3562</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8527</v>
+        <v>1.8666</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5884</v>
+        <v>2.9543</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2643</v>
+        <v>-1.0877</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4648</v>
+        <v>-3.3877</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1577</v>
+        <v>-3.1191</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3071</v>
+        <v>-0.2686</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1094</v>
+        <v>-0.1766</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.383</v>
+        <v>-0.1169</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2736</v>
+        <v>-0.0597</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.252</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5383</v>
+        <v>-2.3152</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8098</v>
+        <v>-2.2357</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7285</v>
+        <v>-0.0795</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.521</v>
+        <v>-3.3175</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1648</v>
+        <v>-1.7462</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3562</v>
+        <v>-1.5714</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8666</v>
+        <v>-1.8527</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9543</v>
+        <v>-0.5884</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0877</v>
+        <v>-1.2643</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3877</v>
+        <v>-1.4648</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.1191</v>
+        <v>-1.1577</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2686</v>
+        <v>-0.3071</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7653</v>
+        <v>-0.1094</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.383</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2567</v>
+        <v>0.2736</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.252</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.731</v>
+        <v>-2.5855</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4483</v>
+        <v>-0.0566</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2827</v>
+        <v>-2.5289</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5214</v>
@@ -1390,13 +1390,13 @@
         <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0423</v>
+        <v>0.1032</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3109</v>
+        <v>0.0809</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2686</v>
+        <v>0.0224</v>
       </c>
       <c r="V12" t="n">
         <v>0.315</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.273</v>
+        <v>-6.9786</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.4187</v>
+        <v>-5.2228</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8543</v>
+        <v>-1.7558</v>
       </c>
       <c r="G13" t="n">
         <v>-6.1612</v>
@@ -1468,13 +1468,13 @@
         <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7973</v>
+        <v>-0.503</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7996</v>
+        <v>-0.6037</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0022</v>
+        <v>0.1007</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3144</v>
@@ -1504,10 +1504,10 @@
         <v>-12.9738</v>
       </c>
       <c r="E14" t="n">
-        <v>4.477100000000001</v>
+        <v>4.477099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.4509</v>
+        <v>-17.4508</v>
       </c>
       <c r="G14" t="n">
         <v>-15.8849</v>
@@ -1546,10 +1546,10 @@
         <v>12.0437</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9702000000000001</v>
+        <v>0.9700000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3729000000000001</v>
+        <v>-0.3727</v>
       </c>
       <c r="U14" t="n">
         <v>1.3429</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5793</v>
+        <v>7.8076</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1619</v>
+        <v>7.1757</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4174</v>
+        <v>0.6319</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7412</v>
+        <v>8.923400000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5322</v>
+        <v>0.0395</v>
       </c>
       <c r="I15" t="n">
-        <v>0.209</v>
+        <v>8.883900000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9467</v>
+        <v>10.1933</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8223</v>
+        <v>2.0009</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1244</v>
+        <v>8.192500000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2056</v>
+        <v>-1.27</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2901</v>
+        <v>-1.9614</v>
       </c>
       <c r="O15" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.6914</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6676</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1694</v>
+        <v>-0.1433</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2151</v>
+        <v>-0.2552</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9543</v>
+        <v>0.1119</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0011</v>
+        <v>0.8804</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0011</v>
+        <v>-0.0629</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9337</v>
+        <v>6.9729</v>
       </c>
       <c r="E16" t="n">
-        <v>6.686</v>
+        <v>4.8681</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2477</v>
+        <v>2.1048</v>
       </c>
       <c r="G16" t="n">
-        <v>8.923400000000001</v>
+        <v>4.7412</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0395</v>
+        <v>4.5322</v>
       </c>
       <c r="I16" t="n">
-        <v>8.883900000000001</v>
+        <v>0.209</v>
       </c>
       <c r="J16" t="n">
-        <v>10.1933</v>
+        <v>4.9467</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0009</v>
+        <v>4.8223</v>
       </c>
       <c r="L16" t="n">
-        <v>8.192500000000001</v>
+        <v>0.1244</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.27</v>
+        <v>-0.2056</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9614</v>
+        <v>-0.2901</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6914</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0172</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7449</v>
+        <v>-0.0786</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2724</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8804</v>
+        <v>0.0011</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0629</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2188</v>
+        <v>2.8768</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9133</v>
+        <v>3.4236</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6945</v>
+        <v>-0.5468</v>
       </c>
       <c r="G17" t="n">
         <v>1.0269</v>
@@ -1780,13 +1780,13 @@
         <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.2453</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4514</v>
+        <v>-0.0382</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1358</v>
+        <v>0.2835</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0629</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0668</v>
+        <v>2.3189</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9513</v>
+        <v>2.2451</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1155</v>
+        <v>0.0738</v>
       </c>
       <c r="G18" t="n">
         <v>3.9053</v>
@@ -1858,13 +1858,13 @@
         <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4606</v>
+        <v>-0.2086</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U18" t="n">
-        <v>0.196</v>
+        <v>0.1542</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0073</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7838</v>
+        <v>1.9075</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4935</v>
+        <v>1.3956</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2903</v>
+        <v>0.5119</v>
       </c>
       <c r="G19" t="n">
         <v>0.0273</v>
@@ -1936,13 +1936,13 @@
         <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0047</v>
+        <v>0.1284</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3109</v>
+        <v>-0.4088</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3156</v>
+        <v>0.5372</v>
       </c>
       <c r="V19" t="n">
         <v>1.196</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5969</v>
+        <v>1.05</v>
       </c>
       <c r="E20" t="n">
-        <v>1.297</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2999</v>
+        <v>0.5364</v>
       </c>
       <c r="G20" t="n">
         <v>1.1872</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7247</v>
+        <v>0.1778</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9774</v>
+        <v>0.194</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2527</v>
+        <v>-0.0162</v>
       </c>
       <c r="V20" t="n">
         <v>-0.315</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.777</v>
+        <v>-0.9593</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8802</v>
+        <v>2.272</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6573</v>
+        <v>-3.2312</v>
       </c>
       <c r="G22" t="n">
         <v>0.1529</v>
@@ -2170,13 +2170,13 @@
         <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8389</v>
+        <v>-0.0211</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.526</v>
+        <v>-0.1343</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3129</v>
+        <v>0.1131</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2027</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. SANTOS PARRA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6554</v>
+        <v>-2.3906</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6993</v>
+        <v>-1.6476</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.956</v>
+        <v>-0.743</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1729</v>
+        <v>-0.7221</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.408</v>
+        <v>0.0412</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.765</v>
+        <v>-0.7633</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5899</v>
+        <v>0.7101</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0215</v>
+        <v>1.2279</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5178</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.583</v>
+        <v>-1.4322</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4294</v>
+        <v>-1.1867</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1536</v>
+        <v>-0.2456</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.2234</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2236</v>
+        <v>-0.0497</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1094</v>
+        <v>-0.1343</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1142</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>-0.6923</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>-0.6923</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>H. SANTOS PARRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6913</v>
+        <v>-2.5328</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0393</v>
+        <v>-0.6014</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.652</v>
+        <v>-1.9314</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7221</v>
+        <v>-1.1729</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0412</v>
+        <v>-0.408</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7633</v>
+        <v>-0.765</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7101</v>
+        <v>-0.5899</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2279</v>
+        <v>0.0215</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5178</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4322</v>
+        <v>-0.583</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1867</v>
+        <v>-0.4294</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2456</v>
+        <v>-0.1536</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2234</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3504</v>
+        <v>-0.101</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.526</v>
+        <v>-0.0115</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1756</v>
+        <v>-0.0895</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6923</v>
+        <v>-1.2589</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6923</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.726</v>
+        <v>-3.4156</v>
       </c>
       <c r="E25" t="n">
         <v>-2.8378</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8881</v>
+        <v>-0.5777</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8282</v>
@@ -2404,13 +2404,13 @@
         <v>2.2234</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5653</v>
+        <v>-0.2549</v>
       </c>
       <c r="T25" t="n">
         <v>-0.1131</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4522</v>
+        <v>-0.1418</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.9737</v>
+        <v>14.2795</v>
       </c>
       <c r="E26" t="n">
-        <v>17.45089999999999</v>
+        <v>17.45099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.4771</v>
+        <v>-3.1713</v>
       </c>
       <c r="G26" t="n">
         <v>15.8851</v>
@@ -2458,7 +2458,7 @@
         <v>27.0624</v>
       </c>
       <c r="K26" t="n">
-        <v>23.53119999999999</v>
+        <v>23.5312</v>
       </c>
       <c r="L26" t="n">
         <v>3.531300000000001</v>
@@ -2482,16 +2482,16 @@
         <v>14.823</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.97</v>
+        <v>0.3359</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.343</v>
+        <v>-1.3428</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3729000000000001</v>
+        <v>1.6785</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.7205</v>
+        <v>-4.720499999999999</v>
       </c>
       <c r="W26" t="n">
         <v>3.7749</v>
